--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127703717</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>127703910</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,48 +1227,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703836</v>
+        <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>79042</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R7" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,6 +1317,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1324,57 +1348,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703628</v>
+        <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R8" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,21 +1429,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1448,7 +1448,7 @@
         <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -1227,42 +1227,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703628</v>
+        <v>127703644</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,21 +1322,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,48 +1338,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703836</v>
+        <v>127703628</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R8" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,6 +1428,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1445,62 +1459,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703644</v>
+        <v>127703836</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R9" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,47 +1227,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703644</v>
+        <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,6 +1317,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1338,42 +1348,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703628</v>
+        <v>127703644</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1428,21 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127703717</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>127703910</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,62 +1348,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703644</v>
+        <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>79047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R8" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,48 +1445,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703836</v>
+        <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R9" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127703717</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>127703910</v>
       </c>
       <c r="B5" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,42 +1227,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703628</v>
+        <v>127703644</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,21 +1322,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,48 +1338,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703836</v>
+        <v>127703628</v>
       </c>
       <c r="B8" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R8" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,6 +1428,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1445,62 +1459,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703644</v>
+        <v>127703836</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>79053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R9" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -1227,47 +1227,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703644</v>
+        <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,6 +1317,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1338,57 +1348,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703628</v>
+        <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R8" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,21 +1429,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,48 +1445,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703836</v>
+        <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>79053</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R9" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -1227,57 +1227,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703628</v>
+        <v>127703836</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R7" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,21 +1308,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,48 +1324,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703836</v>
+        <v>127703644</v>
       </c>
       <c r="B8" t="n">
-        <v>79053</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R8" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,47 +1435,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703644</v>
+        <v>127703628</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1540,6 +1525,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -1227,48 +1227,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703836</v>
+        <v>127703644</v>
       </c>
       <c r="B7" t="n">
-        <v>79053</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R7" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,47 +1338,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703644</v>
+        <v>127703628</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1419,6 +1428,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1435,57 +1459,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703628</v>
+        <v>127703836</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R9" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,21 +1540,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -1227,62 +1227,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703644</v>
+        <v>127703836</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>79053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R7" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,42 +1324,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703628</v>
+        <v>127703644</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1428,21 +1419,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,48 +1435,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703836</v>
+        <v>127703628</v>
       </c>
       <c r="B9" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R9" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,6 +1525,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,48 +1227,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703836</v>
+        <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>79053</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R7" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,6 +1317,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1324,62 +1348,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703644</v>
+        <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>79056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R8" t="n">
-        <v>6681580</v>
+        <v>6681516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,42 +1445,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703628</v>
+        <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,21 +1540,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127703663</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127703717</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127703782</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>127703910</v>
       </c>
       <c r="B5" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127704148</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>127703628</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>127703836</v>
       </c>
       <c r="B8" t="n">
-        <v>79056</v>
+        <v>79067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>127703644</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33885-2025 artfynd.xlsx
+++ b/artfynd/A 33885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127703663</v>
+        <v>127703782</v>
       </c>
       <c r="B2" t="n">
-        <v>98490</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näsberget Näset 2, Dlr</t>
+          <t>Näsberget Näset 5, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507506</v>
+        <v>507464</v>
       </c>
       <c r="R2" t="n">
-        <v>6681575</v>
+        <v>6681516</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,59 +787,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127703717</v>
+        <v>127704148</v>
       </c>
       <c r="B3" t="n">
-        <v>56875</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näsberget Näset 3, Dlr</t>
+          <t>Näsberget Näset 10, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507426</v>
+        <v>507486</v>
       </c>
       <c r="R3" t="n">
-        <v>6681502</v>
+        <v>6681396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,48 +893,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127703782</v>
+        <v>127703628</v>
       </c>
       <c r="B4" t="n">
-        <v>91371</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näsberget Näset 5, Dlr</t>
+          <t>Näsberget Näset 1, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>507464</v>
       </c>
       <c r="R4" t="n">
-        <v>6681516</v>
+        <v>6681580</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127703910</v>
+        <v>127703836</v>
       </c>
       <c r="B5" t="n">
-        <v>56875</v>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,41 +1025,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näsberget Näset 5, Dlr</t>
+          <t>Näsberget Näset 6, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507464</v>
+        <v>507429</v>
       </c>
       <c r="R5" t="n">
         <v>6681516</v>
@@ -1090,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Balgrop, funnen stjärtfjäder intill</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127704148</v>
+        <v>127703717</v>
       </c>
       <c r="B6" t="n">
-        <v>92661</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,43 +1122,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näsberget Näset 10, Dlr</t>
+          <t>Näsberget Näset 3, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507486</v>
+        <v>507426</v>
       </c>
       <c r="R6" t="n">
-        <v>6681396</v>
+        <v>6681502</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,57 +1222,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127703628</v>
+        <v>127703732</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 4, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507464</v>
+        <v>507490</v>
       </c>
       <c r="R7" t="n">
-        <v>6681580</v>
+        <v>6681500</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,21 +1303,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127703836</v>
+        <v>127703910</v>
       </c>
       <c r="B8" t="n">
-        <v>79067</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,31 +1330,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Näset 6, Dlr</t>
+          <t>Näsberget Näset 5, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507429</v>
+        <v>507464</v>
       </c>
       <c r="R8" t="n">
         <v>6681516</v>
@@ -1419,6 +1400,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Balgrop, funnen stjärtfjäder intill</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,62 +1431,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127703644</v>
+        <v>127703989</v>
       </c>
       <c r="B9" t="n">
-        <v>98490</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Näset 1, Dlr</t>
+          <t>Näsberget Näset 7, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507464</v>
+        <v>507497</v>
       </c>
       <c r="R9" t="n">
-        <v>6681580</v>
+        <v>6681442</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,6 +1535,228 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127703644</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näsberget Näset 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>507464</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6681580</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127703663</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näsberget Näset 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>507506</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6681575</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
